--- a/src/nodes/HPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_3_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0010844401625948121</v>
       </c>
       <c r="B2">
-        <v>0.0012192917930723237</v>
+        <v>0.0011550929354467109</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0021688803251896241</v>
       </c>
       <c r="B3">
-        <v>0.0018261526344694832</v>
+        <v>0.0017376623172017465</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0032533204877844366</v>
       </c>
       <c r="B4">
-        <v>0.002336020108672066</v>
+        <v>0.0022287906653946912</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0043377606503792483</v>
       </c>
       <c r="B5">
-        <v>0.0027776276456358004</v>
+        <v>0.0026553027952951054</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.00542220081297406</v>
       </c>
       <c r="B6">
-        <v>0.00316273624993606</v>
+        <v>0.0030281821405062606</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0065066409755688732</v>
       </c>
       <c r="B7">
-        <v>0.0034980866859638</v>
+        <v>0.0033537260115191789</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0075910811381636849</v>
       </c>
       <c r="B8">
-        <v>0.0037876693304644349</v>
+        <v>0.0036356644134642613</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0086755213007584965</v>
       </c>
       <c r="B9">
-        <v>0.0040376747380255979</v>
+        <v>0.0038797802503517933</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0097599614633533081</v>
       </c>
       <c r="B10">
-        <v>0.0042547778738791023</v>
+        <v>0.0040923082559325193</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.01084440162594812</v>
       </c>
       <c r="B11">
-        <v>0.0044453911679912667</v>
+        <v>0.0042792375840391408</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.011928841788542933</v>
       </c>
       <c r="B12">
-        <v>0.0046129588498157268</v>
+        <v>0.004443786801647683</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.013013281951137747</v>
       </c>
       <c r="B13">
-        <v>0.00474931488202086</v>
+        <v>0.0045783377082255113</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.014097722113732556</v>
       </c>
       <c r="B14">
-        <v>0.0048495891250992518</v>
+        <v>0.0046783480096645224</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.01518216227632737</v>
       </c>
       <c r="B15">
-        <v>0.0049337052976255614</v>
+        <v>0.0047624158050633856</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.016266602438922181</v>
       </c>
       <c r="B16">
-        <v>0.0050199372084499868</v>
+        <v>0.0048475990513331549</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.017351042601516993</v>
       </c>
       <c r="B17">
-        <v>0.0050951651694427945</v>
+        <v>0.0049216547434276243</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.018435482764111805</v>
       </c>
       <c r="B18">
-        <v>0.0051424361425159775</v>
+        <v>0.0049687617925721255</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.019519922926706616</v>
       </c>
       <c r="B19">
-        <v>0.0051608571867283676</v>
+        <v>0.0049880877370353958</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.020604363089301428</v>
       </c>
       <c r="B20">
-        <v>0.005153550385425509</v>
+        <v>0.0049825472718470253</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.02168880325189624</v>
       </c>
       <c r="B21">
-        <v>0.0051236378219529435</v>
+        <v>0.0049550550920366039</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.022773243414491051</v>
       </c>
       <c r="B22">
-        <v>0.0050736843468908539</v>
+        <v>0.0049080055633627115</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.023857683577085866</v>
       </c>
       <c r="B23">
-        <v>0.00500402587975798</v>
+        <v>0.0048417117344998831</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.024942123739680678</v>
       </c>
       <c r="B24">
-        <v>0.0049144411073077021</v>
+        <v>0.0047559663248516442</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.026026563902275493</v>
       </c>
       <c r="B25">
-        <v>0.0048047087162933991</v>
+        <v>0.0046505620538215232</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.027111004064870298</v>
       </c>
       <c r="B26">
-        <v>0.004674512868441472</v>
+        <v>0.004525203177807747</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.028195444227465113</v>
       </c>
       <c r="B27">
-        <v>0.0045231596253703975</v>
+        <v>0.0043792401011873584</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.029279884390059924</v>
       </c>
       <c r="B28">
-        <v>0.0043498605236716725</v>
+        <v>0.0042119347653321012</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.03036432455265474</v>
       </c>
       <c r="B29">
-        <v>0.0041538270999367955</v>
+        <v>0.0040225491116137194</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.031448764715249551</v>
       </c>
       <c r="B30">
-        <v>0.0039346801196460529</v>
+        <v>0.0038107267763567033</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.032533204877844363</v>
       </c>
       <c r="B31">
-        <v>0.0036936772638348895</v>
+        <v>0.00357763817569653</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.033617645040439174</v>
       </c>
       <c r="B32">
-        <v>0.0034324854424275376</v>
+        <v>0.0033248354207214168</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.034702085203033986</v>
       </c>
       <c r="B33">
-        <v>0.0031527715653482317</v>
+        <v>0.0030538706225195847</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.0357865253656288</v>
       </c>
       <c r="B34">
-        <v>0.0028555318558418862</v>
+        <v>0.0027656696350134829</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.036870965528223609</v>
       </c>
       <c r="B35">
-        <v>0.002539079790436142</v>
+        <v>0.0024586532834624765</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.037955405690818421</v>
       </c>
       <c r="B36">
-        <v>0.0022010581589793224</v>
+        <v>0.002130616135960159</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.039039845853413233</v>
       </c>
       <c r="B37">
-        <v>0.0018391097513197467</v>
+        <v>0.0017793527606001218</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.040124286016008044</v>
       </c>
       <c r="B38">
-        <v>0.0014492382298741703</v>
+        <v>0.0014011275951251057</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.041208726178602856</v>
       </c>
       <c r="B39">
-        <v>0.001020890747333078</v>
+        <v>0.000986084555874435</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.042293166341197674</v>
       </c>
       <c r="B40">
-        <v>0.00054187532895538771</v>
+        <v>0.00052283742883658154</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.043377606503792479</v>
       </c>
       <c r="B42">
-        <v>1.9268230006977E-17</v>
+        <v>1.9261175492695708E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.042293166341197674</v>
       </c>
       <c r="B43">
-        <v>-2.9261674608795617E-05</v>
+        <v>-1.0223774489989413E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.041208726178602856</v>
       </c>
       <c r="B44">
-        <v>-2.3294996426212548E-05</v>
+        <v>1.1511195032430546E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.040124286016008044</v>
       </c>
       <c r="B45">
-        <v>5.9191874022344526E-06</v>
+        <v>5.4029822151299E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.039039845853413233</v>
       </c>
       <c r="B46">
-        <v>4.640002973101116E-05</v>
+        <v>0.00010615702045063567</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.037955405690818421</v>
       </c>
       <c r="B47">
-        <v>8.7797468404428593E-05</v>
+        <v>0.00015823949142359175</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.036870965528223609</v>
       </c>
       <c r="B48">
-        <v>0.00012628458122617854</v>
+        <v>0.0002067110881998441</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.0357865253656288</v>
       </c>
       <c r="B49">
-        <v>0.00015966523098979857</v>
+        <v>0.00024952745181820165</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.034702085203033986</v>
       </c>
       <c r="B50">
-        <v>0.00018574328048882568</v>
+        <v>0.00028464422331747272</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.033617645040439174</v>
       </c>
       <c r="B51">
-        <v>0.00020298479124390213</v>
+        <v>0.00031063481295002344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.032533204877844363</v>
       </c>
       <c r="B52">
-        <v>0.00021250461968409017</v>
+        <v>0.00032854370782245022</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.031448764715249551</v>
       </c>
       <c r="B53">
-        <v>0.00021607982096555714</v>
+        <v>0.000340033164254907</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.03036432455265474</v>
       </c>
       <c r="B54">
-        <v>0.00021548745024447033</v>
+        <v>0.00034676543856754786</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.029279884390059924</v>
       </c>
       <c r="B55">
-        <v>0.00021208777348448397</v>
+        <v>0.00035001353182405689</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.028195444227465113</v>
       </c>
       <c r="B56">
-        <v>0.00020557389987919971</v>
+        <v>0.00034949342406223968</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.027111004064870298</v>
       </c>
       <c r="B57">
-        <v>0.00019522214942970615</v>
+        <v>0.00034453184006343182</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.026026563902275493</v>
       </c>
       <c r="B58">
-        <v>0.00018030884213709195</v>
+        <v>0.00033445550460896908</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.024942123739680678</v>
       </c>
       <c r="B59">
-        <v>0.00016019763362597013</v>
+        <v>0.00031867241608202809</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.023857683577085866</v>
       </c>
       <c r="B60">
-        <v>0.00013460152201505215</v>
+        <v>0.00029691566727314996</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.022773243414491051</v>
       </c>
       <c r="B61">
-        <v>0.00010332084104657392</v>
+        <v>0.00026899962457471683</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.02168880325189624</v>
       </c>
       <c r="B62">
-        <v>6.61559244627714E-05</v>
+        <v>0.0002347386543791107</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.020604363089301428</v>
       </c>
       <c r="B63">
-        <v>2.3456978071015909E-05</v>
+        <v>0.00019446009164949925</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.019519922926706616</v>
       </c>
       <c r="B64">
-        <v>-2.2226304060780176E-05</v>
+        <v>0.00015054314563219163</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.018435482764111805</v>
       </c>
       <c r="B65">
-        <v>-6.77943557995689E-05</v>
+        <v>0.00010587999414428283</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.017351042601516993</v>
       </c>
       <c r="B66">
-        <v>-0.0001101476110123026</v>
+        <v>6.3362815002867474E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.016266602438922181</v>
       </c>
       <c r="B67">
-        <v>-0.00015020750505497052</v>
+        <v>2.2130652061861503E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.01518216227632737</v>
       </c>
       <c r="B68">
-        <v>-0.00020497947923971065</v>
+        <v>-3.3689986677534796E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.014097722113732556</v>
       </c>
       <c r="B69">
-        <v>-0.00028764433794263388</v>
+        <v>-0.00011640322250790425</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.013013281951137747</v>
       </c>
       <c r="B70">
-        <v>-0.00038000033183959245</v>
+        <v>-0.00020902315804424392</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.011928841788542933</v>
       </c>
       <c r="B71">
-        <v>-0.00046220259522559553</v>
+        <v>-0.00029303054705755117</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.01084440162594812</v>
       </c>
       <c r="B72">
-        <v>-0.0005392163505725337</v>
+        <v>-0.00037306276662040676</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0097599614633533081</v>
       </c>
       <c r="B73">
-        <v>-0.00061931066451837856</v>
+        <v>-0.00045684104657179567</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0086755213007584965</v>
       </c>
       <c r="B74">
-        <v>-0.00069915989218854091</v>
+        <v>-0.00054126540451473614</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0075910811381636849</v>
       </c>
       <c r="B75">
-        <v>-0.00077247817954078431</v>
+        <v>-0.0006204732625406101</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0065066409755688732</v>
       </c>
       <c r="B76">
-        <v>-0.00083273354737484141</v>
+        <v>-0.00068837287293021978</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.00542220081297406</v>
       </c>
       <c r="B77">
-        <v>-0.00087388703295790545</v>
+        <v>-0.0007393329235281063</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0043377606503792483</v>
       </c>
       <c r="B78">
-        <v>-0.00089211786458504255</v>
+        <v>-0.00076979301424434762</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0032533204877844366</v>
       </c>
       <c r="B79">
-        <v>-0.0008808631896491839</v>
+        <v>-0.00077363374637180889</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0021688803251896241</v>
       </c>
       <c r="B80">
-        <v>-0.00082855688356261569</v>
+        <v>-0.000740066566294879</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0010844401625948121</v>
       </c>
       <c r="B81">
-        <v>-0.0007066739356960623</v>
+        <v>-0.0006424750780704494</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0012585760113802914</v>
       </c>
       <c r="B2">
-        <v>0.00058934003288346065</v>
+        <v>0.00046081425060130537</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0025171520227605828</v>
       </c>
       <c r="B3">
-        <v>0.00088280913009054643</v>
+        <v>0.0007056519707286567</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0037757280341408745</v>
       </c>
       <c r="B4">
-        <v>0.0011296143437610003</v>
+        <v>0.000914941550651887</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0050343040455211657</v>
       </c>
       <c r="B5">
-        <v>0.0013436085059076095</v>
+        <v>0.0010987147856132324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0062928800569014565</v>
       </c>
       <c r="B6">
-        <v>0.0015304398304375243</v>
+        <v>0.0012610631964389135</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.007551456068281749</v>
       </c>
       <c r="B7">
-        <v>0.0016933323648962188</v>
+        <v>0.00140432303825094</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.00881003207966204</v>
       </c>
       <c r="B8">
-        <v>0.00183418184216878</v>
+        <v>0.0015298687813023026</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.010068608091042331</v>
       </c>
       <c r="B9">
-        <v>0.0019559516183025958</v>
+        <v>0.0016398476672843214</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.011327184102422621</v>
       </c>
       <c r="B10">
-        <v>0.0020618410458905743</v>
+        <v>0.0017365777076324095</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.012585760113802913</v>
       </c>
       <c r="B11">
-        <v>0.0021549258405454074</v>
+        <v>0.0018222872213200232</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.013844336125183205</v>
       </c>
       <c r="B12">
-        <v>0.002236847985092087</v>
+        <v>0.0018981664160543576</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.015102912136563498</v>
       </c>
       <c r="B13">
-        <v>0.002303638168185026</v>
+        <v>0.0019613427469395237</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.016361488147943786</v>
       </c>
       <c r="B14">
-        <v>0.00235292247805764</v>
+        <v>0.0020100986470096434</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.017620064159324079</v>
       </c>
       <c r="B15">
-        <v>0.002394319895429927</v>
+        <v>0.002051399213621971</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.018878640170704369</v>
       </c>
       <c r="B16">
-        <v>0.0024366529015394105</v>
+        <v>0.002091632798694639</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.020137216182084663</v>
       </c>
       <c r="B17">
-        <v>0.0024735650872071231</v>
+        <v>0.0021261981080661629</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.021395792193464953</v>
       </c>
       <c r="B18">
-        <v>0.0024968480618744542</v>
+        <v>0.0021491529078726357</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.022654368204845243</v>
       </c>
       <c r="B19">
-        <v>0.0025060643998807107</v>
+        <v>0.0021601808515200687</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.023912944216225536</v>
       </c>
       <c r="B20">
-        <v>0.0025027194167896796</v>
+        <v>0.0021603720642319559</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.025171520227605826</v>
       </c>
       <c r="B21">
-        <v>0.0024883184281651485</v>
+        <v>0.0021508166712317909</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.026430096238986119</v>
       </c>
       <c r="B22">
-        <v>0.0024640987382385485</v>
+        <v>0.0021324106670163132</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.027688672250366409</v>
       </c>
       <c r="B23">
-        <v>0.0024302256059118964</v>
+        <v>0.0021052735231752492</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.028947248261746703</v>
       </c>
       <c r="B24">
-        <v>0.0023865962787548538</v>
+        <v>0.0020693305805715716</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.030205824273126996</v>
       </c>
       <c r="B25">
-        <v>0.0023331080043370823</v>
+        <v>0.0020245071800682533</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.031464400284507282</v>
       </c>
       <c r="B26">
-        <v>0.0022696137425927639</v>
+        <v>0.0019706965110289731</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.032722976295887572</v>
       </c>
       <c r="B27">
-        <v>0.0021957893029141591</v>
+        <v>0.0019076631568202287</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.033981552307267869</v>
       </c>
       <c r="B28">
-        <v>0.0021112662070580488</v>
+        <v>0.0018351395493092244</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.035240128318648159</v>
       </c>
       <c r="B29">
-        <v>0.0020156759767812151</v>
+        <v>0.0017528581203631645</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.036498704330028449</v>
       </c>
       <c r="B30">
-        <v>0.0019088495342752978</v>
+        <v>0.0016606955794859792</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.037757280341408739</v>
       </c>
       <c r="B31">
-        <v>0.0017914154034713789</v>
+        <v>0.0015591057467285059</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.039015856352789029</v>
       </c>
       <c r="B32">
-        <v>0.0016642015087353981</v>
+        <v>0.001448686719778308</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.040274432364169326</v>
       </c>
       <c r="B33">
-        <v>0.0015280357744332964</v>
+        <v>0.0013300365963229489</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.041533008375549615</v>
       </c>
       <c r="B34">
-        <v>0.0013834235166079113</v>
+        <v>0.0012035198133841577</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.042791584386929905</v>
       </c>
       <c r="B35">
-        <v>0.0012295796180096666</v>
+        <v>0.0010685661653203221</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.044050160398310195</v>
       </c>
       <c r="B36">
-        <v>0.0010653963530658818</v>
+        <v>0.00092437178582399551</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.045308736409690485</v>
       </c>
       <c r="B37">
-        <v>0.0008897659962038766</v>
+        <v>0.00077013280858772985</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.046567312421070782</v>
       </c>
       <c r="B38">
-        <v>0.00070078989781784552</v>
+        <v>0.00060447265486510485</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.047825888432451072</v>
       </c>
       <c r="B39">
-        <v>0.00049340571216948347</v>
+        <v>0.00042372389615380685</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.049084464443831362</v>
       </c>
       <c r="B40">
-        <v>0.00026176016948735963</v>
+        <v>0.00022364639151254881</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1335,7 +1335,7 @@
         <v>0.050343040455211652</v>
       </c>
       <c r="B41">
-        <v>4.4626270860279654E-17</v>
+        <v>4.4713602114409358E-17</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.050343040455211652</v>
       </c>
       <c r="B42">
-        <v>4.4708143911026249E-17</v>
+        <v>4.4702685707643147E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.049084464443831362</v>
       </c>
       <c r="B43">
-        <v>-1.4426627431558778E-05</v>
+        <v>2.3687150543251956E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.047825888432451072</v>
       </c>
       <c r="B44">
-        <v>-1.1534983596288544E-05</v>
+        <v>5.8146832419387972E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.046567312421070782</v>
       </c>
       <c r="B45">
-        <v>2.8388619284201571E-06</v>
+        <v>9.9156104881160842E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.045308736409690485</v>
       </c>
       <c r="B46">
-        <v>2.2858839565131972E-05</v>
+        <v>0.00014249202718127869</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.044050160398310195</v>
       </c>
       <c r="B47">
-        <v>4.3479199139168732E-05</v>
+        <v>0.00018450376638105514</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.042791584386929905</v>
       </c>
       <c r="B48">
-        <v>6.2815468086881011E-05</v>
+        <v>0.00022382892077622542</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.041533008375549615</v>
       </c>
       <c r="B49">
-        <v>7.9773493247376886E-05</v>
+        <v>0.00025967719647113064</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.040274432364169326</v>
       </c>
       <c r="B50">
-        <v>9.32591214597641E-05</v>
+        <v>0.00029125829957011158</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.039015856352789029</v>
       </c>
       <c r="B51">
-        <v>0.00010250013948112202</v>
+        <v>0.00031801492843821209</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.037757280341408739</v>
       </c>
       <c r="B52">
-        <v>0.0001080120937404159</v>
+        <v>0.00034032175048328872</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.036498704330028449</v>
       </c>
       <c r="B53">
-        <v>0.00011063247058458242</v>
+        <v>0.00035878642537390108</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.035240128318648159</v>
       </c>
       <c r="B54">
-        <v>0.00011119875636055837</v>
+        <v>0.00037401661277860891</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.033981552307267869</v>
       </c>
       <c r="B55">
-        <v>0.00011034839728395684</v>
+        <v>0.0003864750550327815</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.032722976295887572</v>
       </c>
       <c r="B56">
-        <v>0.00010791867904509665</v>
+        <v>0.00039604482513902727</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.031464400284507282</v>
       </c>
       <c r="B57">
-        <v>0.000103546847202973</v>
+        <v>0.00040246407876676416</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.030205824273126996</v>
       </c>
       <c r="B58">
-        <v>9.6870147316581147E-05</v>
+        <v>0.00040547097158541033</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.028947248261746703</v>
       </c>
       <c r="B59">
-        <v>8.7569480325271393E-05</v>
+        <v>0.00040483517850855379</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.027688672250366409</v>
       </c>
       <c r="B60">
-        <v>7.5500368689814863E-05</v>
+        <v>0.00040045245142646211</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.026430096238986119</v>
       </c>
       <c r="B61">
-        <v>6.0561990251337782E-05</v>
+        <v>0.00039225006147357278</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.025171520227605826</v>
       </c>
       <c r="B62">
-        <v>4.2653522850966359E-05</v>
+        <v>0.00038015527978432339</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.023912944216225536</v>
       </c>
       <c r="B63">
-        <v>2.1941499704725009E-05</v>
+        <v>0.0003642888522624487</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.022654368204845243</v>
       </c>
       <c r="B64">
-        <v>-3.3812447176966335E-07</v>
+        <v>0.00034554542388887262</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.021395792193464953</v>
       </c>
       <c r="B65">
-        <v>-2.2682039588002724E-05</v>
+        <v>0.00032501311441381628</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.020137216182084663</v>
       </c>
       <c r="B66">
-        <v>-4.3586935553459436E-05</v>
+        <v>0.00030378004358750093</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.018878640170704369</v>
       </c>
       <c r="B67">
-        <v>-6.3492771248791985E-05</v>
+        <v>0.00028152733159597995</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.017620064159324079</v>
       </c>
       <c r="B68">
-        <v>-9.06125814393207E-05</v>
+        <v>0.00025230810036863547</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.016361488147943786</v>
       </c>
       <c r="B69">
-        <v>-0.00013130818171045008</v>
+        <v>0.00021151564933754631</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.015102912136563498</v>
       </c>
       <c r="B70">
-        <v>-0.00017676343504325216</v>
+        <v>0.0001655319862022503</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.013844336125183205</v>
       </c>
       <c r="B71">
-        <v>-0.00021736628329725307</v>
+        <v>0.00012131528574047581</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.012585760113802913</v>
       </c>
       <c r="B72">
-        <v>-0.00025549893645012681</v>
+        <v>7.7139682775256846E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.011327184102422621</v>
       </c>
       <c r="B73">
-        <v>-0.000295139666125109</v>
+        <v>3.01236721330552E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.010068608091042331</v>
       </c>
       <c r="B74">
-        <v>-0.000334656722409535</v>
+        <v>-1.8552771391261009E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.00881003207966204</v>
       </c>
       <c r="B75">
-        <v>-0.00037098526555931813</v>
+        <v>-6.6672204692840655E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.007551456068281749</v>
       </c>
       <c r="B76">
-        <v>-0.00040093811804058581</v>
+        <v>-0.00011192879139530679</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0062928800569014565</v>
       </c>
       <c r="B77">
-        <v>-0.0004215647637553067</v>
+        <v>-0.00015218812975669596</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0050343040455211657</v>
       </c>
       <c r="B78">
-        <v>-0.000430983670138601</v>
+        <v>-0.00018608994984422388</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0037757280341408745</v>
       </c>
       <c r="B79">
-        <v>-0.00042598560630503985</v>
+        <v>-0.00021131281319592635</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0025171520227605828</v>
       </c>
       <c r="B80">
-        <v>-0.0004009384015173505</v>
+        <v>-0.0002237812421554608</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0012585760113802914</v>
       </c>
       <c r="B81">
-        <v>-0.00034200621553795489</v>
+        <v>-0.00021348043325579961</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0014097722113732558</v>
       </c>
       <c r="B2">
-        <v>0.00039230797208870987</v>
+        <v>0.00028798482844708895</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0028195444227465116</v>
       </c>
       <c r="B3">
-        <v>0.00058598682690500946</v>
+        <v>0.00044219006134493745</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0042293166341197674</v>
       </c>
       <c r="B4">
-        <v>0.000748519388454098</v>
+        <v>0.00057427154312836358</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0056390888454930232</v>
       </c>
       <c r="B5">
-        <v>0.000889211935381428</v>
+        <v>0.000690434053577799</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0070488610568662782</v>
       </c>
       <c r="B6">
-        <v>0.0010118568110633463</v>
+        <v>0.000793206383239923</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.0084586332682395349</v>
       </c>
       <c r="B7">
-        <v>0.001118617411913284</v>
+        <v>0.000884031315940774</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.00986840547961279</v>
       </c>
       <c r="B8">
-        <v>0.0012107645445121669</v>
+        <v>0.00096375655438688413</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.011278177690986047</v>
       </c>
       <c r="B9">
-        <v>0.0012902868594203271</v>
+        <v>0.0010337083169503943</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0126879499023593</v>
       </c>
       <c r="B10">
-        <v>0.001359331769964729</v>
+        <v>0.0010953186408015317</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.014097722113732556</v>
       </c>
       <c r="B11">
-        <v>0.0014199638965594621</v>
+        <v>0.0011499643226372562</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.015507494325105814</v>
       </c>
       <c r="B12">
-        <v>0.0014732844257758814</v>
+        <v>0.00119837984750281</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.01691726653647907</v>
       </c>
       <c r="B13">
-        <v>0.0015166236017272762</v>
+        <v>0.001238785694309835</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.018327038747852326</v>
       </c>
       <c r="B14">
-        <v>0.0015483840569645935</v>
+        <v>0.0012701172443831579</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.019736810959225581</v>
       </c>
       <c r="B15">
-        <v>0.0015750289202474774</v>
+        <v>0.0012966834948339417</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.021146583170598834</v>
       </c>
       <c r="B16">
-        <v>0.0016024861425661479</v>
+        <v>0.0013224366372512958</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.022556355381972093</v>
       </c>
       <c r="B17">
-        <v>0.0016264824676244288</v>
+        <v>0.0013445280253497776</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.023966127593345349</v>
       </c>
       <c r="B18">
-        <v>0.0016415001355036822</v>
+        <v>0.0013592793168449235</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.0253758998047186</v>
       </c>
       <c r="B19">
-        <v>0.001647244579081817</v>
+        <v>0.0013664942233307382</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.02678567201609186</v>
       </c>
       <c r="B20">
-        <v>0.0016447270294358783</v>
+        <v>0.0013668469698708433</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.028195444227465113</v>
       </c>
       <c r="B21">
-        <v>0.0016349587176429116</v>
+        <v>0.0013610117815288604</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.029605216438838369</v>
       </c>
       <c r="B22">
-        <v>0.0016187709005582311</v>
+        <v>0.0013495428773249991</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.031014988650211628</v>
       </c>
       <c r="B23">
-        <v>0.0015962749381502263</v>
+        <v>0.0013325144521058173</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.032424760861584884</v>
       </c>
       <c r="B24">
-        <v>0.0015674022161655549</v>
+        <v>0.001309880694674461</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.03383453307295814</v>
       </c>
       <c r="B25">
-        <v>0.0015320841203508753</v>
+        <v>0.0012815957938340753</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.035244305284331388</v>
       </c>
       <c r="B26">
-        <v>0.0014902224170594823</v>
+        <v>0.001247594169779678</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.036654077495704651</v>
       </c>
       <c r="B27">
-        <v>0.0014416003950712142</v>
+        <v>0.0012077311682737741</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.038063849707077907</v>
       </c>
       <c r="B28">
-        <v>0.0013859717237725468</v>
+        <v>0.0011618423664707409</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.039473621918451163</v>
       </c>
       <c r="B29">
-        <v>0.0013230900725499553</v>
+        <v>0.0011097633415249545</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.040883394129824419</v>
       </c>
       <c r="B30">
-        <v>0.0012528432712922641</v>
+        <v>0.0010514190884470707</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.042293166341197667</v>
       </c>
       <c r="B31">
-        <v>0.0011756557918976929</v>
+        <v>0.000987092273672858</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.043702938552570923</v>
       </c>
       <c r="B32">
-        <v>0.0010920862667668097</v>
+        <v>0.00091715498149436277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.045112710763944186</v>
       </c>
       <c r="B33">
-        <v>0.0010026933283001831</v>
+        <v>0.0008419792962036318</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.046522482975317442</v>
       </c>
       <c r="B34">
-        <v>0.00090781894531464851</v>
+        <v>0.0007617928364684935</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.0479322551866907</v>
       </c>
       <c r="B35">
-        <v>0.00080693843229211041</v>
+        <v>0.00067624535845990392</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.049342027398063946</v>
       </c>
       <c r="B36">
-        <v>0.000699310440130741</v>
+        <v>0.00058484215272460068</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.0507517996094372</v>
       </c>
       <c r="B37">
-        <v>0.00058419361972871062</v>
+        <v>0.00048708850980932068</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.052161571820810458</v>
       </c>
       <c r="B38">
-        <v>0.00046031519895798175</v>
+        <v>0.00038213541749075185</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.053571344032183721</v>
       </c>
       <c r="B39">
-        <v>0.00032427671358567777</v>
+        <v>0.00026771665246538281</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.054981116243556977</v>
       </c>
       <c r="B40">
-        <v>0.00017214827635271234</v>
+        <v>0.00014121168865965242</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2001,7 +2001,7 @@
         <v>0.056390888454930226</v>
       </c>
       <c r="B41">
-        <v>-4.8911299016978481E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2009,7 +2009,7 @@
         <v>0.056390888454930226</v>
       </c>
       <c r="B42">
-        <v>3.0569561885611551E-21</v>
+        <v>6.11391237712231E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.054981116243556977</v>
       </c>
       <c r="B43">
-        <v>-1.3471249805647229E-05</v>
+        <v>1.746533788741272E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.053571344032183721</v>
       </c>
       <c r="B44">
-        <v>-1.508365313609168E-05</v>
+        <v>4.1476407984203259E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.052161571820810458</v>
       </c>
       <c r="B45">
-        <v>-8.763489845397391E-06</v>
+        <v>6.9416291621832491E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.0507517996094372</v>
       </c>
       <c r="B46">
-        <v>1.5629602123714978E-06</v>
+        <v>9.8668070131761372E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.049342027398063946</v>
       </c>
       <c r="B47">
-        <v>1.2500715693900314E-05</v>
+        <v>0.00012696900310004043</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.0479322551866907</v>
       </c>
       <c r="B48">
-        <v>2.27799892988722E-05</v>
+        <v>0.0001534730631310786</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.046522482975317442</v>
       </c>
       <c r="B49">
-        <v>3.16622922377199E-05</v>
+        <v>0.00017768840108387467</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.045112710763944186</v>
       </c>
       <c r="B50">
-        <v>3.840913572087601E-05</v>
+        <v>0.00019912316781742722</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.043702938552570923</v>
       </c>
       <c r="B51">
-        <v>4.2498555132128056E-05</v>
+        <v>0.00021742984040457503</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.042293166341197667</v>
       </c>
       <c r="B52">
-        <v>4.4274682548683056E-05</v>
+        <v>0.00023283820077351809</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.040883394129824419</v>
       </c>
       <c r="B53">
-        <v>4.4298174221102905E-05</v>
+        <v>0.00024572235706629648</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.039473621918451163</v>
       </c>
       <c r="B54">
-        <v>4.31296863999495E-05</v>
+        <v>0.00025645641742495052</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.038063849707077907</v>
       </c>
       <c r="B55">
-        <v>4.1195579961710263E-05</v>
+        <v>0.00026532493726351641</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.036654077495704651</v>
       </c>
       <c r="B56">
-        <v>3.8385034286574759E-05</v>
+        <v>0.00027225426108401474</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.035244305284331388</v>
       </c>
       <c r="B57">
-        <v>3.4452933380658084E-05</v>
+        <v>0.00027708118066046216</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.03383453307295814</v>
       </c>
       <c r="B58">
-        <v>2.9154161250075357E-05</v>
+        <v>0.00027964248776687548</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.032424760861584884</v>
       </c>
       <c r="B59">
-        <v>2.2273087218991949E-05</v>
+        <v>0.00027979460871008585</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.031014988650211628</v>
       </c>
       <c r="B60">
-        <v>1.3712021883774535E-05</v>
+        <v>0.00027747250792818325</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.029605216438838369</v>
       </c>
       <c r="B61">
-        <v>3.402761158840101E-06</v>
+        <v>0.00027263078439207207</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.028195444227465113</v>
       </c>
       <c r="B62">
-        <v>-8.7228990413943677E-06</v>
+        <v>0.00026522403707265673</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.02678567201609186</v>
       </c>
       <c r="B63">
-        <v>-2.2553327954331944E-05</v>
+        <v>0.00025532673161070323</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.0253758998047186</v>
       </c>
       <c r="B64">
-        <v>-3.7257555424656083E-05</v>
+        <v>0.00024349280032642283</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.023966127593345349</v>
       </c>
       <c r="B65">
-        <v>-5.1824776448870216E-05</v>
+        <v>0.00023039604220988861</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.022556355381972093</v>
       </c>
       <c r="B66">
-        <v>-6.5244186023477872E-05</v>
+        <v>0.00021671025625117331</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.021146583170598834</v>
       </c>
       <c r="B67">
-        <v>-7.78108893229636E-05</v>
+        <v>0.00020223861599188837</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.019736810959225581</v>
       </c>
       <c r="B68">
-        <v>-9.5043632233736235E-05</v>
+        <v>0.00018330179317979943</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.018327038747852326</v>
       </c>
       <c r="B69">
-        <v>-0.00012121681852401944</v>
+        <v>0.00015704999405741611</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.01691726653647907</v>
       </c>
       <c r="B70">
-        <v>-0.00015040384277737094</v>
+        <v>0.00012743406464007034</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.015507494325105814</v>
       </c>
       <c r="B71">
-        <v>-0.0001761430438625483</v>
+        <v>9.8761534410523428E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.014097722113732556</v>
       </c>
       <c r="B72">
-        <v>-0.00020003354697377317</v>
+        <v>6.9966026948432771E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0126879499023593</v>
       </c>
       <c r="B73">
-        <v>-0.00022474700501445231</v>
+        <v>3.9266124148744609E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.011278177690986047</v>
       </c>
       <c r="B74">
-        <v>-0.00024918439539926818</v>
+        <v>7.3941470706644744E-06</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.00986840547961279</v>
       </c>
       <c r="B75">
-        <v>-0.0002712833962395294</v>
+        <v>-2.4275406114246555E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.0084586332682395349</v>
       </c>
       <c r="B76">
-        <v>-0.0002888991639217745</v>
+        <v>-5.4313067949264616E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0070488610568662782</v>
       </c>
       <c r="B77">
-        <v>-0.00030004575587719258</v>
+        <v>-8.1395328053769346E-05</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0056390888454930232</v>
       </c>
       <c r="B78">
-        <v>-0.000303455355440346</v>
+        <v>-0.00010467747363671691</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0042293166341197674</v>
       </c>
       <c r="B79">
-        <v>-0.0002969676835003083</v>
+        <v>-0.00012271983817457391</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0028195444227465116</v>
       </c>
       <c r="B80">
-        <v>-0.00027679376645542273</v>
+        <v>-0.0001329970008953507</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0014097722113732558</v>
       </c>
       <c r="B81">
-        <v>-0.00023363088976101557</v>
+        <v>-0.00012930774611939465</v>
       </c>
     </row>
     <row r="82" spans="1:2">
